--- a/datasets/mp/04 Histórico mensual de demanda por categoría - sintético.xlsx
+++ b/datasets/mp/04 Histórico mensual de demanda por categoría - sintético.xlsx
@@ -12806,7 +12806,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>DATOS 100 % FICTICIOS para el programa IA-abilities (Coknow). Marcas, referencias, zonas, códigos de asesora, cifras y comentarios son inventados. No corresponden a la Compañía ni a ninguna empresa o persona real.</t>
+          <t>DATOS 100 % FICTICIOS para el programa IA-abilities. Marcas, referencias, zonas, códigos de asesora, cifras y comentarios son inventados. No corresponden a la Compañía ni a ninguna empresa o persona real.</t>
         </is>
       </c>
     </row>

--- a/datasets/mp/04 Histórico mensual de demanda por categoría - sintético.xlsx
+++ b/datasets/mp/04 Histórico mensual de demanda por categoría - sintético.xlsx
@@ -5178,7 +5178,6 @@
           <t>Tirsa Casa</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
       <c r="E132" s="2" t="n">
         <v>100400</v>
       </c>
@@ -8090,7 +8089,6 @@
           <t>Nórdika</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
       <c r="E213" s="2" t="n">
         <v>105500</v>
       </c>
@@ -12848,24 +12846,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>- Loop: un rol pronostica, otro revisa supuestos (¿trató el quiebre como demanda real?) y la condición de parada es que el error en los últimos 6 meses (retroprueba) quede documentado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Sembrados: Hogar tuvo quiebre de inventario en noviembre y diciembre de 2024 (las ventas bajas no son demanda baja);</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Calzado tiene un pico atípico en marzo de 2025 sin explicación en los datos; hay dos meses sin dato.</t>
-        </is>
-      </c>
-    </row>
+          <t>- Loop: un rol pronostica, otro revisa supuestos (¿trató los datos raros como demanda real?) y la condición de parada es que el error en los últimos 6 meses (retroprueba) quede documentado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
